--- a/assets/constructions/examples/ctd_mt3.xlsx
+++ b/assets/constructions/examples/ctd_mt3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,59 +654,84 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D3T06024L100-I40UNTMVTH</t>
+          <t>M1C121150290-EI2M</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MilliPro HD</t>
+          <t>M1C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UNC 5-40-3xDo</t>
+          <t>M14.0X2.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>40</v>
-      </c>
-      <c r="N2" t="n">
-        <v>40</v>
-      </c>
-      <c r="O2" t="n">
-        <v>40</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Coarse</t>
@@ -720,30 +745,32 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>2.45</v>
+        <v>11.5</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>1.905</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AC2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -753,13 +780,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+          <t>ALCRSIN</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Super MG</t>
+        </is>
+      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>VTH</t>
+          <t>Super MG</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -780,7 +811,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -796,65 +827,84 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2018/VARGUS2018-ENGweb.pdf</t>
+          <t>2023/Amati Форма Точности</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1044.16</v>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AW2" t="n">
+        <v>12822.91</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D3T06052L132-I28UNTMVTH</t>
+          <t>M3C161600480-I2.5M</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MilliPro HD</t>
+          <t>M3C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UNF 1/4"x28-2xD</t>
+          <t>M20X2.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>28</v>
-      </c>
-      <c r="N3" t="n">
-        <v>28</v>
-      </c>
-      <c r="O3" t="n">
-        <v>28</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -868,27 +918,29 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
-        <v>5.25</v>
+        <v>16</v>
       </c>
       <c r="W3" t="n">
-        <v>6</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
-        <v>2.721</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>13.2</v>
+        <v>48</v>
       </c>
       <c r="AB3" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="AC3" t="n">
-        <v>43.8</v>
+        <v>52</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -898,13 +950,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+          <t>ALCRSIN</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Super MG</t>
+        </is>
+      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>VTH</t>
+          <t>Super MG</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -925,7 +981,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-16</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -941,65 +997,80 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>2018/VARGUS2018-ENGweb.pdf</t>
+          <t>2023/Amati Форма Точности</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2437.76</v>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AW3" t="n">
+        <v>29937.16</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D3T06014L039-I72UNTMVTH</t>
+          <t>R217.13-031070AC12P 1620</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MilliPro HD</t>
+          <t>CoroMillⓇ Plura solid carbide end mill for thread milling</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMKNSH</t>
+          <t>PMKNSHO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UNF 1-72-2xDo</t>
+          <t>M 4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>M60</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>72</v>
-      </c>
-      <c r="N4" t="n">
-        <v>72</v>
-      </c>
-      <c r="O4" t="n">
-        <v>72</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1010,31 +1081,35 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>3.1</v>
       </c>
       <c r="W4" t="n">
         <v>6</v>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="Y4" t="n">
-        <v>1.058</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AA4" t="n">
-        <v>3.9</v>
+        <v>13.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>57</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>53.1</v>
-      </c>
+        <v>56.65</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
@@ -1043,13 +1118,17 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>TiAlN</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+          <t>PVD ALCRN</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>VTH</t>
+          <t>1620</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1057,7 +1136,9 @@
           <t>VHM</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AJ4" t="n">
+        <v>15</v>
+      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>HA</t>
@@ -1078,66 +1159,85 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>COROMANT</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.028</v>
+      </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>2018/VARGUS2018-ENGweb.pdf</t>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>PMKNSHO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7081TC-M3</t>
+          <t>M1C101000280-EI2M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ILIX</t>
+          <t>AMATI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7081TC</t>
+          <t>M1C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PMH</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
+          <t>M14.0X2.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>M60</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>M60</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4H-6H/6G-7G</t>
+          <t>Standard</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1154,28 +1254,34 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="n">
-        <v>6.2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="AB5" t="n">
-        <v>39</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>45</v>
+      </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
@@ -1184,17 +1290,17 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>ALCRSIN</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>K 20</t>
+          <t>Super MG</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>K 20</t>
+          <t>Super MG</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1202,9 +1308,7 @@
           <t>VHM</t>
         </is>
       </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
           <t>HA</t>
@@ -1212,12 +1316,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>HA-3</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1233,35 +1337,54 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>2019/ilix_katalog_taps.pdf</t>
+          <t>2023/Amati Форма Точности</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>732.16</v>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AW5" t="n">
+        <v>8991.360000000001</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M3C040073025-I0.25M</t>
+          <t>D3T06019L052-I0.45ISOTMLVTH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMATI</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M3C</t>
+          <t>MilliPro HD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMK</t>
+          <t>PMKNSH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M1.0X0.25</t>
+          <t>M2.5X0.45-2xDo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1271,20 +1394,20 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="K6" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1308,26 +1431,24 @@
         <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>0.73</v>
+        <v>1.95</v>
       </c>
       <c r="W6" t="n">
-        <v>4</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>1.35</v>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AC6" t="n">
-        <v>47.5</v>
+        <v>94.8</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1337,17 +1458,13 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ALCRSIN</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Super MG</t>
-        </is>
-      </c>
+          <t>TiAlN</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Super MG</t>
+          <t>VTH</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1368,7 +1485,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -1384,7 +1501,26 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>2023/Amati Форма Точности</t>
+          <t>2018/VARGUS2018-ENGweb.pdf</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>173.88</v>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AW6" t="n">
+        <v>15985.43</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
